--- a/research/MFT.NZ/Reports/MFT.NZ_DCF_Model.xlsx
+++ b/research/MFT.NZ/Reports/MFT.NZ_DCF_Model.xlsx
@@ -2080,9 +2080,10 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="5">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B9" s="5">
         <v>63.927</v>
